--- a/data/trans_orig/LAWTONB_2R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/LAWTONB_2R-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el nivel de dependencia funcional para actividades instrumentales de la vida diaria (Lawton y Brody) en 2007</t>
+          <t>Población según el grado de dependencia funcional para actividades instrumentales de la vida diaria (Lawton y Brody) en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>71803</t>
+          <t>71113</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>90297</t>
+          <t>89576</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>62,44%</t>
+          <t>61,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>77,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>92178</t>
+          <t>90853</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>114890</t>
+          <t>114197</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>61,64%</t>
+          <t>60,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,83%</t>
+          <t>76,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>168981</t>
+          <t>168435</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>198059</t>
+          <t>199583</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>63,88%</t>
+          <t>63,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>74,87%</t>
+          <t>75,45%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8056</t>
+          <t>7898</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21955</t>
+          <t>22660</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12504</t>
+          <t>12784</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28499</t>
+          <t>29824</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>24641</t>
+          <t>24420</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>47338</t>
+          <t>46594</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,61%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2507</t>
+          <t>2169</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11448</t>
+          <t>12245</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6112</t>
+          <t>6077</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>20371</t>
+          <t>19601</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>10813</t>
+          <t>10099</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>27120</t>
+          <t>26657</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,08%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2834</t>
+          <t>2799</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13177</t>
+          <t>13240</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1976</t>
+          <t>1846</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11136</t>
+          <t>11671</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5899</t>
+          <t>6054</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19483</t>
+          <t>19984</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,55%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3599</t>
+          <t>3637</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13929</t>
+          <t>14546</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4508</t>
+          <t>3525</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>16944</t>
+          <t>16794</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>9564</t>
+          <t>10041</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>25586</t>
+          <t>26795</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>10,13%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>87344</t>
+          <t>86134</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>109452</t>
+          <t>108748</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>59,87%</t>
+          <t>59,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>75,02%</t>
+          <t>74,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>99766</t>
+          <t>98946</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>126780</t>
+          <t>127105</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>54,61%</t>
+          <t>54,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>69,4%</t>
+          <t>69,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>193782</t>
+          <t>194920</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>228345</t>
+          <t>228874</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>58,98%</t>
+          <t>59,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>69,5%</t>
+          <t>69,66%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19639</t>
+          <t>19740</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>38001</t>
+          <t>38952</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21552</t>
+          <t>21414</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>42404</t>
+          <t>44118</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>46331</t>
+          <t>46361</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>73259</t>
+          <t>74123</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,56%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3830</t>
+          <t>3769</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14425</t>
+          <t>14595</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12973</t>
+          <t>13485</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>31893</t>
+          <t>31004</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>19065</t>
+          <t>18892</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>40779</t>
+          <t>39954</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,16%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3840</t>
+          <t>3932</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15402</t>
+          <t>15471</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1220</t>
+          <t>1224</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10804</t>
+          <t>12109</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7357</t>
+          <t>7525</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21568</t>
+          <t>21386</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,51%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>940</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8832</t>
+          <t>8691</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5964</t>
+          <t>6084</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>20718</t>
+          <t>21598</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8617</t>
+          <t>8759</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>24466</t>
+          <t>25184</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,66%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>72617</t>
+          <t>73577</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>89954</t>
+          <t>90767</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>69,58%</t>
+          <t>70,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>77447</t>
+          <t>78626</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>99744</t>
+          <t>99573</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>57,01%</t>
+          <t>57,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>73,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>158334</t>
+          <t>157016</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>188152</t>
+          <t>185686</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>65,91%</t>
+          <t>65,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>77,3%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5334</t>
+          <t>5324</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17570</t>
+          <t>17470</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19039</t>
+          <t>18733</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>38409</t>
+          <t>37894</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>26627</t>
+          <t>28078</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>50382</t>
+          <t>49433</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,58%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3528</t>
+          <t>3316</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15785</t>
+          <t>14487</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2257</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>13024</t>
+          <t>12574</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7597</t>
+          <t>7492</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>24304</t>
+          <t>22581</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>9,4%</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4916</t>
+          <t>4940</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2173</t>
+          <t>2517</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12155</t>
+          <t>13759</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3064</t>
+          <t>2919</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14511</t>
+          <t>13961</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,81%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>878</t>
+          <t>884</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7495</t>
+          <t>7560</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2551</t>
+          <t>2561</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13402</t>
+          <t>13396</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4582</t>
+          <t>4423</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>17315</t>
+          <t>16848</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,01%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>99641</t>
+          <t>98846</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>116638</t>
+          <t>116225</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>72,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>122683</t>
+          <t>123439</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>149715</t>
+          <t>150222</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>58,76%</t>
+          <t>59,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>71,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>227833</t>
+          <t>227529</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>261516</t>
+          <t>260745</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>65,85%</t>
+          <t>65,76%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>75,36%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>9164</t>
+          <t>9286</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>22589</t>
+          <t>22650</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>20267</t>
+          <t>19148</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>40373</t>
+          <t>39440</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>32944</t>
+          <t>32554</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>56931</t>
+          <t>56737</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,4%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>2551</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>11114</t>
+          <t>11653</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>16434</t>
+          <t>17155</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>36470</t>
+          <t>36911</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>21576</t>
+          <t>21317</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>44554</t>
+          <t>43200</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,49%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1612</t>
+          <t>1619</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9435</t>
+          <t>9156</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4407</t>
+          <t>4834</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>17481</t>
+          <t>16871</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>7697</t>
+          <t>7993</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>21953</t>
+          <t>22236</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,43%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>826</t>
+          <t>836</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>8225</t>
+          <t>7609</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>4046</t>
+          <t>3447</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>16495</t>
+          <t>15246</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6337</t>
+          <t>6545</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>19710</t>
+          <t>19364</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>350705</t>
+          <t>349507</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>387769</t>
+          <t>387323</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>69,8%</t>
+          <t>69,56%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>77,08%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>419435</t>
+          <t>416568</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>468948</t>
+          <t>466891</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>61,97%</t>
+          <t>61,55%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>68,98%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>784114</t>
+          <t>783585</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>848876</t>
+          <t>846564</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>66,44%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>71,98%</t>
+          <t>71,78%</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>54696</t>
+          <t>54191</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>85743</t>
+          <t>84918</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>89343</t>
+          <t>89243</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>127370</t>
+          <t>127226</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>152566</t>
+          <t>149667</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>200229</t>
+          <t>198546</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,84%</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>18763</t>
+          <t>18223</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>37949</t>
+          <t>39547</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>49479</t>
+          <t>49585</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>80589</t>
+          <t>79493</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>71607</t>
+          <t>73686</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>110888</t>
+          <t>110932</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,41%</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>13779</t>
+          <t>12850</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>30022</t>
+          <t>29573</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>16379</t>
+          <t>17548</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>36832</t>
+          <t>39582</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3850,12 +3850,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>34821</t>
+          <t>34279</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>60266</t>
+          <t>60627</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,14%</t>
         </is>
       </c>
     </row>
@@ -3913,12 +3913,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>10802</t>
+          <t>11014</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>26520</t>
+          <t>27032</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3928,12 +3928,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>25095</t>
+          <t>25012</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>50026</t>
+          <t>49328</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3963,12 +3963,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>41749</t>
+          <t>40948</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>68780</t>
+          <t>69230</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,87%</t>
         </is>
       </c>
     </row>
@@ -4180,7 +4180,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el nivel de dependencia funcional para actividades instrumentales de la vida diaria (Lawton y Brody) en 2012</t>
+          <t>Población según el grado de dependencia funcional para actividades instrumentales de la vida diaria (Lawton y Brody) en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4375,12 +4375,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>93562</t>
+          <t>94515</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>114224</t>
+          <t>114838</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4390,12 +4390,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>67,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>82,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>91341</t>
+          <t>92276</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>116588</t>
+          <t>116348</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4425,12 +4425,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>55,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>69,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>192234</t>
+          <t>192553</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>226217</t>
+          <t>225389</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4460,12 +4460,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>62,75%</t>
+          <t>62,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>73,85%</t>
+          <t>73,58%</t>
         </is>
       </c>
     </row>
@@ -4488,12 +4488,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>4617</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16452</t>
+          <t>17320</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4503,12 +4503,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10450</t>
+          <t>9946</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26008</t>
+          <t>26193</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4538,12 +4538,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18946</t>
+          <t>17856</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>38571</t>
+          <t>38210</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,47%</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4601,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8276</t>
+          <t>8229</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23160</t>
+          <t>23321</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4616,12 +4616,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13397</t>
+          <t>13036</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>32207</t>
+          <t>31062</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>24846</t>
+          <t>24797</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>47322</t>
+          <t>47892</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,63%</t>
         </is>
       </c>
     </row>
@@ -4714,12 +4714,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1893</t>
+          <t>1887</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14401</t>
+          <t>14808</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4729,12 +4729,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5698</t>
+          <t>6427</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19539</t>
+          <t>20674</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10118</t>
+          <t>10042</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28853</t>
+          <t>27238</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>8,89%</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1972</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10774</t>
+          <t>11234</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4842,12 +4842,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5622</t>
+          <t>6279</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>19150</t>
+          <t>19322</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>10121</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>26579</t>
+          <t>25223</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,23%</t>
         </is>
       </c>
     </row>
@@ -5057,12 +5057,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>96438</t>
+          <t>96259</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>121848</t>
+          <t>120274</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>62,27%</t>
+          <t>62,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>78,67%</t>
+          <t>77,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>89074</t>
+          <t>87373</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>115663</t>
+          <t>117330</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>45,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,42%</t>
+          <t>61,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>192928</t>
+          <t>191274</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>229850</t>
+          <t>228802</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,71%</t>
+          <t>55,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>66,07%</t>
         </is>
       </c>
     </row>
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4138</t>
+          <t>4089</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16139</t>
+          <t>15716</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20328</t>
+          <t>19984</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>40858</t>
+          <t>40207</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>26707</t>
+          <t>27931</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>51015</t>
+          <t>50402</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,55%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4170</t>
+          <t>4179</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16610</t>
+          <t>15358</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5318,7 +5318,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6385</t>
+          <t>6551</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -5333,7 +5333,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>12456</t>
+          <t>12697</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>31356</t>
+          <t>30544</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,82%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8586</t>
+          <t>8935</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25563</t>
+          <t>25127</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5411,12 +5411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17553</t>
+          <t>16264</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37063</t>
+          <t>38121</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>30243</t>
+          <t>30616</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>55821</t>
+          <t>56779</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,4%</t>
         </is>
       </c>
     </row>
@@ -5509,12 +5509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6926</t>
+          <t>6507</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>23623</t>
+          <t>21950</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5524,12 +5524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14382</t>
+          <t>14587</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>32293</t>
+          <t>33132</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>24959</t>
+          <t>25756</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>48349</t>
+          <t>50113</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,47%</t>
         </is>
       </c>
     </row>
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>64411</t>
+          <t>65042</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>85828</t>
+          <t>85055</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>62,17%</t>
+          <t>62,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>82,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>76546</t>
+          <t>75508</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>99620</t>
+          <t>99240</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>54,28%</t>
+          <t>53,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>70,64%</t>
+          <t>70,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>146869</t>
+          <t>147463</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>178151</t>
+          <t>179497</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>60,04%</t>
+          <t>60,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>72,83%</t>
+          <t>73,38%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1692</t>
+          <t>1093</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13756</t>
+          <t>12896</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5175</t>
+          <t>5926</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18828</t>
+          <t>20099</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9412</t>
+          <t>8655</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>27289</t>
+          <t>25762</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>10,53%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3000</t>
+          <t>2522</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13220</t>
+          <t>13744</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5353</t>
+          <t>5252</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>17866</t>
+          <t>18917</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>9664</t>
+          <t>10513</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>26489</t>
+          <t>27148</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>11,1%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3185</t>
+          <t>4089</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16339</t>
+          <t>17423</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7097</t>
+          <t>7434</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>20779</t>
+          <t>21249</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>12855</t>
+          <t>13727</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>31176</t>
+          <t>31712</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,96%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3141</t>
+          <t>3203</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>16801</t>
+          <t>16741</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>11467</t>
+          <t>10929</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>28980</t>
+          <t>28062</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>16139</t>
+          <t>16484</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>38545</t>
+          <t>38218</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,62%</t>
         </is>
       </c>
     </row>
@@ -6421,12 +6421,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>106094</t>
+          <t>106768</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>130141</t>
+          <t>131187</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>65,65%</t>
+          <t>66,06%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>80,53%</t>
+          <t>81,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>145687</t>
+          <t>145844</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>176256</t>
+          <t>176357</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>59,77%</t>
+          <t>59,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>72,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>259327</t>
+          <t>262027</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>298068</t>
+          <t>299514</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>63,97%</t>
+          <t>64,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>73,53%</t>
+          <t>73,89%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>5051</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>17527</t>
+          <t>17840</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>24669</t>
+          <t>24877</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>47518</t>
+          <t>47539</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>33055</t>
+          <t>33286</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>58296</t>
+          <t>59458</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,67%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6431</t>
+          <t>6120</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>22615</t>
+          <t>20961</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>7165</t>
+          <t>7137</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>21738</t>
+          <t>21656</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>16950</t>
+          <t>17335</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>38330</t>
+          <t>37738</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,31%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5997</t>
+          <t>5877</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>20327</t>
+          <t>20445</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>9260</t>
+          <t>9557</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>26565</t>
+          <t>26007</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>17414</t>
+          <t>17953</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>40584</t>
+          <t>39317</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,7%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3437</t>
+          <t>3027</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>16198</t>
+          <t>16475</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>11429</t>
+          <t>11192</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>27934</t>
+          <t>27161</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6923,12 +6923,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>17179</t>
+          <t>16592</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>38296</t>
+          <t>37348</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,21%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>386166</t>
+          <t>387230</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>430498</t>
+          <t>431970</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>69,0%</t>
+          <t>69,19%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>77,19%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>427961</t>
+          <t>426598</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>481598</t>
+          <t>482258</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>57,6%</t>
+          <t>57,42%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>64,82%</t>
+          <t>64,91%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>831557</t>
+          <t>831877</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>901661</t>
+          <t>901880</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>63,84%</t>
+          <t>63,86%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>69,22%</t>
+          <t>69,24%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>23130</t>
+          <t>22901</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>45766</t>
+          <t>46736</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>74410</t>
+          <t>75582</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>110566</t>
+          <t>112641</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>106508</t>
+          <t>104504</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>149028</t>
+          <t>148635</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,41%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>30542</t>
+          <t>31323</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>56894</t>
+          <t>56317</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>42123</t>
+          <t>43496</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>73223</t>
+          <t>74613</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>80294</t>
+          <t>82799</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>119440</t>
+          <t>121688</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,34%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>28011</t>
+          <t>29401</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>55415</t>
+          <t>55607</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>52366</t>
+          <t>52979</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>84368</t>
+          <t>84756</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>88349</t>
+          <t>87491</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>131668</t>
+          <t>129725</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>9,96%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>23222</t>
+          <t>22985</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>48479</t>
+          <t>47887</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>55689</t>
+          <t>54544</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>89180</t>
+          <t>87232</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>84662</t>
+          <t>84516</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>126237</t>
+          <t>128250</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,85%</t>
         </is>
       </c>
     </row>
@@ -7822,7 +7822,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el nivel de dependencia funcional para actividades instrumentales de la vida diaria (Lawton y Brody) en 2016</t>
+          <t>Población según el grado de dependencia funcional para actividades instrumentales de la vida diaria (Lawton y Brody) en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8017,12 +8017,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>99206</t>
+          <t>100032</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>117097</t>
+          <t>117159</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8032,12 +8032,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>73,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>98494</t>
+          <t>99878</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>125019</t>
+          <t>125920</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8067,12 +8067,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>57,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>72,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8087,12 +8087,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>205320</t>
+          <t>205589</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>237471</t>
+          <t>236595</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8102,12 +8102,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>66,21%</t>
+          <t>66,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>76,57%</t>
+          <t>76,29%</t>
         </is>
       </c>
     </row>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>807</t>
+          <t>815</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8571</t>
+          <t>8266</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8165,12 +8165,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10851</t>
+          <t>11126</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29429</t>
+          <t>29069</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8180,12 +8180,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>14136</t>
+          <t>13897</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>33264</t>
+          <t>33307</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8215,12 +8215,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,74%</t>
         </is>
       </c>
     </row>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5085</t>
+          <t>5305</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16972</t>
+          <t>16958</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13182</t>
+          <t>12769</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>31471</t>
+          <t>30471</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>20627</t>
+          <t>20930</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>42018</t>
+          <t>43535</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>14,04%</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8356,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4017</t>
+          <t>4412</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14991</t>
+          <t>14205</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5953</t>
+          <t>5459</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20071</t>
+          <t>19508</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12141</t>
+          <t>11748</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29278</t>
+          <t>30164</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,73%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2444</t>
+          <t>2456</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11630</t>
+          <t>11704</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3821</t>
+          <t>4636</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>17100</t>
+          <t>17868</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>8476</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>23832</t>
+          <t>24529</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,91%</t>
         </is>
       </c>
     </row>
@@ -8699,12 +8699,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>113575</t>
+          <t>113313</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>134060</t>
+          <t>134688</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8714,12 +8714,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>68,86%</t>
+          <t>68,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>81,28%</t>
+          <t>81,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8734,12 +8734,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>122499</t>
+          <t>121099</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>154143</t>
+          <t>153158</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8749,12 +8749,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>55,89%</t>
+          <t>55,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>70,33%</t>
+          <t>69,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>245442</t>
+          <t>241921</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>283477</t>
+          <t>281332</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>63,9%</t>
+          <t>62,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>73,8%</t>
+          <t>73,24%</t>
         </is>
       </c>
     </row>
@@ -8812,12 +8812,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8620</t>
+          <t>7742</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21744</t>
+          <t>21362</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8827,12 +8827,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8847,12 +8847,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17088</t>
+          <t>17298</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>38375</t>
+          <t>36870</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8862,12 +8862,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>27806</t>
+          <t>28286</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>53318</t>
+          <t>53151</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,84%</t>
         </is>
       </c>
     </row>
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6172</t>
+          <t>6818</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>19200</t>
+          <t>18996</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>16535</t>
+          <t>16718</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>38617</t>
+          <t>38835</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>25596</t>
+          <t>28007</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>51230</t>
+          <t>52700</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,72%</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4968</t>
+          <t>4896</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16677</t>
+          <t>16429</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11798</t>
+          <t>12354</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31590</t>
+          <t>32152</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9088,12 +9088,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19005</t>
+          <t>19171</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>42446</t>
+          <t>41807</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,88%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2622</t>
+          <t>2587</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11638</t>
+          <t>12143</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3510</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>18087</t>
+          <t>18031</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8173</t>
+          <t>7482</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>24427</t>
+          <t>24940</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,49%</t>
         </is>
       </c>
     </row>
@@ -9381,12 +9381,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>79901</t>
+          <t>78999</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>96844</t>
+          <t>96880</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>69,46%</t>
+          <t>68,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>84,19%</t>
+          <t>84,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9416,12 +9416,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>76178</t>
+          <t>74491</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>99743</t>
+          <t>99921</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>52,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>69,95%</t>
+          <t>70,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>161183</t>
+          <t>161108</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>192019</t>
+          <t>192690</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9466,12 +9466,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>62,56%</t>
+          <t>62,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>74,53%</t>
+          <t>74,79%</t>
         </is>
       </c>
     </row>
@@ -9494,12 +9494,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6631</t>
+          <t>6754</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18687</t>
+          <t>19352</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9509,12 +9509,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7431</t>
+          <t>7377</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22449</t>
+          <t>22362</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>17624</t>
+          <t>16577</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>36302</t>
+          <t>36348</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9579,12 +9579,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,11%</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9607,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1882</t>
+          <t>1822</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11196</t>
+          <t>10941</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8665</t>
+          <t>8631</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>25167</t>
+          <t>26468</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9657,12 +9657,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>13617</t>
+          <t>13288</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>32774</t>
+          <t>33726</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9692,12 +9692,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>13,09%</t>
         </is>
       </c>
     </row>
@@ -9725,7 +9725,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13517</t>
+          <t>14040</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9740,7 +9740,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7569</t>
+          <t>7779</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>23907</t>
+          <t>24353</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9770,12 +9770,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>13645</t>
+          <t>14267</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>32821</t>
+          <t>32790</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,73%</t>
         </is>
       </c>
     </row>
@@ -9838,7 +9838,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6165</t>
+          <t>7773</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9853,7 +9853,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4577</t>
+          <t>3976</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>18592</t>
+          <t>17673</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6173</t>
+          <t>6016</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>20981</t>
+          <t>19885</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,72%</t>
         </is>
       </c>
     </row>
@@ -10063,12 +10063,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>135526</t>
+          <t>134320</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>153780</t>
+          <t>153519</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10078,12 +10078,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>76,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>87,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>140544</t>
+          <t>141905</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>175302</t>
+          <t>175632</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10113,12 +10113,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>57,89%</t>
+          <t>58,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>72,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10133,12 +10133,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>283788</t>
+          <t>283816</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>322354</t>
+          <t>322480</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10148,12 +10148,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>67,99%</t>
+          <t>68,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>77,23%</t>
+          <t>77,26%</t>
         </is>
       </c>
     </row>
@@ -10176,12 +10176,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2705</t>
+          <t>2502</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>11742</t>
+          <t>11876</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10191,12 +10191,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>25154</t>
+          <t>25338</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>49867</t>
+          <t>51194</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10226,12 +10226,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10246,12 +10246,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>30905</t>
+          <t>30821</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>57817</t>
+          <t>56970</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10261,12 +10261,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,65%</t>
         </is>
       </c>
     </row>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7623</t>
+          <t>8103</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>21498</t>
+          <t>22609</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10304,12 +10304,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>7291</t>
+          <t>7618</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>23844</t>
+          <t>23849</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10339,7 +10339,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>19308</t>
+          <t>17693</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>39555</t>
+          <t>39012</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,35%</t>
         </is>
       </c>
     </row>
@@ -10402,12 +10402,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3337</t>
+          <t>3471</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>12639</t>
+          <t>13298</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10417,12 +10417,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10437,12 +10437,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10595</t>
+          <t>11066</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>31364</t>
+          <t>30660</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>16744</t>
+          <t>16737</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>38634</t>
+          <t>38806</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10492,7 +10492,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,3%</t>
         </is>
       </c>
     </row>
@@ -10515,12 +10515,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>787</t>
+          <t>780</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7659</t>
+          <t>8906</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10535,7 +10535,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10550,12 +10550,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>6389</t>
+          <t>6027</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>24742</t>
+          <t>24404</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>9239</t>
+          <t>8551</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>27607</t>
+          <t>26527</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,36%</t>
         </is>
       </c>
     </row>
@@ -10745,12 +10745,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>448531</t>
+          <t>447386</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>485225</t>
+          <t>485687</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10760,12 +10760,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>75,85%</t>
+          <t>75,66%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>82,13%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10780,12 +10780,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>473667</t>
+          <t>471482</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>530242</t>
+          <t>526834</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>60,89%</t>
+          <t>60,61%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>68,16%</t>
+          <t>67,72%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>929173</t>
+          <t>930435</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>998362</t>
+          <t>1001458</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>67,86%</t>
+          <t>67,95%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>72,91%</t>
+          <t>73,14%</t>
         </is>
       </c>
     </row>
@@ -10858,12 +10858,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>26537</t>
+          <t>25483</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>48002</t>
+          <t>46963</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10873,12 +10873,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>75422</t>
+          <t>75655</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>114785</t>
+          <t>117029</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>109525</t>
+          <t>108426</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>155611</t>
+          <t>152714</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,15%</t>
         </is>
       </c>
     </row>
@@ -10971,12 +10971,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>29691</t>
+          <t>28794</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>53727</t>
+          <t>53869</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>60851</t>
+          <t>62970</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>96709</t>
+          <t>99627</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>97890</t>
+          <t>100410</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>144099</t>
+          <t>142731</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,42%</t>
         </is>
       </c>
     </row>
@@ -11084,12 +11084,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>22667</t>
+          <t>22612</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>43336</t>
+          <t>43734</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11099,12 +11099,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11119,12 +11119,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>48168</t>
+          <t>49893</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>83464</t>
+          <t>83183</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11134,12 +11134,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11154,12 +11154,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>77371</t>
+          <t>77475</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>119666</t>
+          <t>117537</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,58%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>9949</t>
+          <t>10612</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>25872</t>
+          <t>25052</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>27247</t>
+          <t>28883</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>57463</t>
+          <t>58050</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>43748</t>
+          <t>44181</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>76316</t>
+          <t>74064</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -11464,7 +11464,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el nivel de dependencia funcional para actividades instrumentales de la vida diaria (Lawton y Brody) en 2023</t>
+          <t>Población según el grado de dependencia funcional para actividades instrumentales de la vida diaria (Lawton y Brody) en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11659,12 +11659,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>88486</t>
+          <t>87503</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>106637</t>
+          <t>106334</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11674,12 +11674,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>59,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>72,01%</t>
+          <t>71,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11694,12 +11694,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>86279</t>
+          <t>87148</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>103171</t>
+          <t>103151</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11709,12 +11709,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>48,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,92%</t>
+          <t>57,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11729,12 +11729,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>179188</t>
+          <t>179536</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>203782</t>
+          <t>204337</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11744,12 +11744,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>54,93%</t>
+          <t>55,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>62,47%</t>
+          <t>62,64%</t>
         </is>
       </c>
     </row>
@@ -11772,12 +11772,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8519</t>
+          <t>8760</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19618</t>
+          <t>20193</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11787,12 +11787,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11807,12 +11807,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15425</t>
+          <t>15660</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26299</t>
+          <t>26892</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11822,12 +11822,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11842,12 +11842,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>26461</t>
+          <t>26635</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>41642</t>
+          <t>41343</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11857,12 +11857,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,67%</t>
         </is>
       </c>
     </row>
@@ -11885,12 +11885,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6087</t>
+          <t>5959</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15208</t>
+          <t>14896</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11900,12 +11900,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11920,12 +11920,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13305</t>
+          <t>13579</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>24275</t>
+          <t>24095</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11935,12 +11935,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11955,12 +11955,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>21693</t>
+          <t>21784</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>36588</t>
+          <t>35784</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11970,12 +11970,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>10,97%</t>
         </is>
       </c>
     </row>
@@ -11998,12 +11998,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12314</t>
+          <t>12142</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24728</t>
+          <t>24778</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -12033,12 +12033,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21215</t>
+          <t>20952</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32941</t>
+          <t>33119</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -12048,12 +12048,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -12068,12 +12068,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>36830</t>
+          <t>36529</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>54037</t>
+          <t>55299</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -12083,12 +12083,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,95%</t>
         </is>
       </c>
     </row>
@@ -12111,12 +12111,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5324</t>
+          <t>5868</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14764</t>
+          <t>15773</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -12126,12 +12126,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12146,12 +12146,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13052</t>
+          <t>13031</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>23016</t>
+          <t>23210</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -12161,12 +12161,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12181,12 +12181,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>20916</t>
+          <t>20702</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>35141</t>
+          <t>34232</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -12196,12 +12196,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,49%</t>
         </is>
       </c>
     </row>
@@ -12341,12 +12341,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>109676</t>
+          <t>108921</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>127460</t>
+          <t>125746</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -12356,12 +12356,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>68,5%</t>
+          <t>68,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>78,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12376,12 +12376,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>116037</t>
+          <t>116259</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>135943</t>
+          <t>136758</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -12391,12 +12391,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>53,34%</t>
+          <t>53,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,5%</t>
+          <t>62,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12411,12 +12411,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>229877</t>
+          <t>230460</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>257912</t>
+          <t>258598</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -12426,12 +12426,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>60,87%</t>
+          <t>61,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>68,3%</t>
+          <t>68,48%</t>
         </is>
       </c>
     </row>
@@ -12454,12 +12454,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7935</t>
+          <t>8154</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18396</t>
+          <t>19459</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -12469,12 +12469,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12489,12 +12489,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20559</t>
+          <t>20253</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>33319</t>
+          <t>33666</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -12504,12 +12504,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12524,12 +12524,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>31346</t>
+          <t>30396</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>49527</t>
+          <t>48091</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -12539,12 +12539,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>12,73%</t>
         </is>
       </c>
     </row>
@@ -12567,12 +12567,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>5570</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14933</t>
+          <t>15642</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -12582,12 +12582,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12602,12 +12602,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>14590</t>
+          <t>14457</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>27287</t>
+          <t>25883</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -12617,12 +12617,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12637,12 +12637,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>21787</t>
+          <t>22381</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>36766</t>
+          <t>37550</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,94%</t>
         </is>
       </c>
     </row>
@@ -12680,12 +12680,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9961</t>
+          <t>9746</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20958</t>
+          <t>20908</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12695,12 +12695,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12715,12 +12715,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17473</t>
+          <t>17301</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29925</t>
+          <t>29390</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12730,12 +12730,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12750,12 +12750,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>29607</t>
+          <t>29273</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>46584</t>
+          <t>46310</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12765,12 +12765,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,26%</t>
         </is>
       </c>
     </row>
@@ -12793,12 +12793,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2465</t>
+          <t>2778</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9709</t>
+          <t>10231</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12808,12 +12808,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15659</t>
+          <t>15795</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>28727</t>
+          <t>29810</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12843,12 +12843,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12863,12 +12863,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>20888</t>
+          <t>20345</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>35205</t>
+          <t>34965</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12878,12 +12878,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,26%</t>
         </is>
       </c>
     </row>
@@ -13023,12 +13023,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>99397</t>
+          <t>98915</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>115287</t>
+          <t>115363</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -13038,12 +13038,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>73,38%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>85,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13058,12 +13058,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>214004</t>
+          <t>210723</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>343089</t>
+          <t>343080</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -13073,7 +13073,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>58,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -13093,12 +13093,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>339291</t>
+          <t>337344</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>462544</t>
+          <t>458295</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -13108,12 +13108,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>68,51%</t>
+          <t>68,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>92,54%</t>
         </is>
       </c>
     </row>
@@ -13136,12 +13136,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10107</t>
+          <t>9655</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22778</t>
+          <t>22147</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -13151,12 +13151,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13171,12 +13171,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6010</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>53800</t>
+          <t>54640</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -13186,12 +13186,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13206,12 +13206,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>12019</t>
+          <t>13549</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>65783</t>
+          <t>67742</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -13221,12 +13221,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,68%</t>
         </is>
       </c>
     </row>
@@ -13249,12 +13249,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1440</t>
+          <t>1744</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8445</t>
+          <t>7700</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13264,12 +13264,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13284,12 +13284,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2860</t>
+          <t>3859</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>35518</t>
+          <t>36902</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -13299,12 +13299,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13319,12 +13319,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5125</t>
+          <t>5757</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>34219</t>
+          <t>34586</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -13334,12 +13334,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,98%</t>
         </is>
       </c>
     </row>
@@ -13362,12 +13362,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2071</t>
+          <t>1965</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9538</t>
+          <t>9292</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -13377,12 +13377,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13397,12 +13397,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2080</t>
+          <t>2470</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>28193</t>
+          <t>30247</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -13412,12 +13412,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13432,12 +13432,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4452</t>
+          <t>5373</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>30010</t>
+          <t>30253</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -13447,12 +13447,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,11%</t>
         </is>
       </c>
     </row>
@@ -13480,7 +13480,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8596</t>
+          <t>8748</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -13495,7 +13495,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13510,12 +13510,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3313</t>
+          <t>4055</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>36548</t>
+          <t>37040</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -13525,12 +13525,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13545,12 +13545,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5470</t>
+          <t>5725</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>34469</t>
+          <t>35784</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -13560,12 +13560,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,23%</t>
         </is>
       </c>
     </row>
@@ -13705,12 +13705,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>148494</t>
+          <t>148546</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>166227</t>
+          <t>165985</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13720,12 +13720,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>73,97%</t>
+          <t>74,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>82,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13740,12 +13740,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>155931</t>
+          <t>155285</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>180236</t>
+          <t>179513</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13755,12 +13755,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>56,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>65,57%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13775,12 +13775,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>309009</t>
+          <t>310575</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>340044</t>
+          <t>341166</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13790,12 +13790,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>65,12%</t>
+          <t>65,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>71,9%</t>
         </is>
       </c>
     </row>
@@ -13818,12 +13818,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>10122</t>
+          <t>10063</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>22558</t>
+          <t>22311</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13833,12 +13833,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13853,12 +13853,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>31049</t>
+          <t>30662</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>47131</t>
+          <t>46534</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13868,12 +13868,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13888,12 +13888,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>44086</t>
+          <t>44530</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>64288</t>
+          <t>66280</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13903,12 +13903,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,97%</t>
         </is>
       </c>
     </row>
@@ -13931,12 +13931,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6299</t>
+          <t>6148</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>16056</t>
+          <t>16604</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13946,82 +13946,82 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
+          <t>8,27%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>27670</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>20759</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>36019</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>10,11%</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>7,58%</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>13,16%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>37977</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>29451</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>47004</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
           <t>8,0%</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>27670</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>21324</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>35802</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>10,11%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>7,79%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>13,08%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>37977</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>28719</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>46595</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>8,0%</t>
-        </is>
-      </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,91%</t>
         </is>
       </c>
     </row>
@@ -14044,12 +14044,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6954</t>
+          <t>7067</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>17068</t>
+          <t>17843</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14079,12 +14079,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>18108</t>
+          <t>17908</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>32603</t>
+          <t>33181</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -14094,12 +14094,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14114,12 +14114,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>27819</t>
+          <t>27830</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>45710</t>
+          <t>45872</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -14129,12 +14129,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,67%</t>
         </is>
       </c>
     </row>
@@ -14157,12 +14157,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2595</t>
+          <t>2707</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>10085</t>
+          <t>10639</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -14172,12 +14172,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14192,12 +14192,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>10005</t>
+          <t>10370</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>21522</t>
+          <t>22342</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -14207,12 +14207,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14227,12 +14227,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>15108</t>
+          <t>15461</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>30018</t>
+          <t>29234</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14242,12 +14242,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,16%</t>
         </is>
       </c>
     </row>
@@ -14387,12 +14387,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>463090</t>
+          <t>463502</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>498424</t>
+          <t>498815</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -14402,12 +14402,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>71,86%</t>
+          <t>71,93%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>77,41%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -14422,12 +14422,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>594718</t>
+          <t>595479</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>850746</t>
+          <t>849988</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>57,78%</t>
+          <t>57,86%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>82,59%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -14457,12 +14457,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1089502</t>
+          <t>1086845</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1321108</t>
+          <t>1328904</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -14472,12 +14472,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>65,1%</t>
+          <t>64,94%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>79,4%</t>
         </is>
       </c>
     </row>
@@ -14500,12 +14500,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>46283</t>
+          <t>44924</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>68569</t>
+          <t>68802</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -14515,12 +14515,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14535,12 +14535,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>56193</t>
+          <t>53081</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>141971</t>
+          <t>139099</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -14550,12 +14550,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14570,12 +14570,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>113357</t>
+          <t>107087</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>192761</t>
+          <t>194789</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -14585,12 +14585,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,64%</t>
         </is>
       </c>
     </row>
@@ -14613,12 +14613,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>24593</t>
+          <t>25098</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>42540</t>
+          <t>42816</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -14628,12 +14628,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14648,12 +14648,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>38930</t>
+          <t>40220</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>103567</t>
+          <t>104551</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14663,12 +14663,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14683,12 +14683,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>74774</t>
+          <t>75234</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>136470</t>
+          <t>135914</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14698,12 +14698,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,12%</t>
         </is>
       </c>
     </row>
@@ -14726,12 +14726,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>38480</t>
+          <t>38881</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>60512</t>
+          <t>60716</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14741,12 +14741,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14761,12 +14761,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>44017</t>
+          <t>45578</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>112253</t>
+          <t>113117</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14776,12 +14776,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14796,12 +14796,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>90869</t>
+          <t>88758</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>160343</t>
+          <t>159873</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -14811,12 +14811,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,55%</t>
         </is>
       </c>
     </row>
@@ -14839,12 +14839,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>18069</t>
+          <t>17695</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>33305</t>
+          <t>32974</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -14854,12 +14854,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14874,12 +14874,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>37882</t>
+          <t>36036</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>91434</t>
+          <t>92701</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -14889,12 +14889,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14909,12 +14909,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>62076</t>
+          <t>61459</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>113380</t>
+          <t>114281</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14924,12 +14924,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,83%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/LAWTONB_2R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/LAWTONB_2R-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>71113</t>
+          <t>71232</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>89576</t>
+          <t>90064</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>61,84%</t>
+          <t>61,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>77,9%</t>
+          <t>78,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>90853</t>
+          <t>92187</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>114197</t>
+          <t>114472</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>60,76%</t>
+          <t>61,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,37%</t>
+          <t>76,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>168435</t>
+          <t>168322</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>199583</t>
+          <t>198886</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>63,67%</t>
+          <t>63,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>75,45%</t>
+          <t>75,19%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7898</t>
+          <t>7875</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22660</t>
+          <t>21729</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12784</t>
+          <t>12807</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29824</t>
+          <t>28772</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>24420</t>
+          <t>24435</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>46594</t>
+          <t>45767</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,3%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2169</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12245</t>
+          <t>12497</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6077</t>
+          <t>6073</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19601</t>
+          <t>19284</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>10099</t>
+          <t>10737</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>26657</t>
+          <t>26515</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,02%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2799</t>
+          <t>2823</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13240</t>
+          <t>13201</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1846</t>
+          <t>1949</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11671</t>
+          <t>12057</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6054</t>
+          <t>6500</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19984</t>
+          <t>20956</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,92%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3637</t>
+          <t>3648</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14546</t>
+          <t>13189</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3525</t>
+          <t>4518</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>16794</t>
+          <t>17902</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>10041</t>
+          <t>10014</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>26795</t>
+          <t>26131</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>9,88%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>86134</t>
+          <t>85886</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>108748</t>
+          <t>108245</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>59,04%</t>
+          <t>58,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>74,54%</t>
+          <t>74,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>98946</t>
+          <t>100698</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>127105</t>
+          <t>127234</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>54,16%</t>
+          <t>55,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>69,58%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>194920</t>
+          <t>192906</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>228874</t>
+          <t>228690</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>59,32%</t>
+          <t>58,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>69,66%</t>
+          <t>69,6%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19740</t>
+          <t>19458</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>38952</t>
+          <t>38583</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21414</t>
+          <t>21293</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>44118</t>
+          <t>41971</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>46361</t>
+          <t>45428</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>74123</t>
+          <t>73559</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,39%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3769</t>
+          <t>3691</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14595</t>
+          <t>14672</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>13485</t>
+          <t>13665</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>31004</t>
+          <t>31263</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>18892</t>
+          <t>19609</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>39954</t>
+          <t>40586</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,35%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3932</t>
+          <t>3856</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15471</t>
+          <t>15740</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1224</t>
+          <t>1217</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12109</t>
+          <t>10981</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7525</t>
+          <t>7207</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21386</t>
+          <t>21069</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,41%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>932</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8691</t>
+          <t>8796</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6084</t>
+          <t>5980</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21598</t>
+          <t>21430</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8759</t>
+          <t>8790</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>25184</t>
+          <t>25371</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,72%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>73577</t>
+          <t>73942</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>90767</t>
+          <t>90482</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>70,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>78626</t>
+          <t>77928</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>99573</t>
+          <t>99656</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>57,88%</t>
+          <t>57,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>73,3%</t>
+          <t>73,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>157016</t>
+          <t>157871</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>185686</t>
+          <t>186421</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>65,36%</t>
+          <t>65,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>77,3%</t>
+          <t>77,6%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5324</t>
+          <t>4672</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17470</t>
+          <t>18161</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18733</t>
+          <t>18754</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>37894</t>
+          <t>37287</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>28078</t>
+          <t>27064</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>49433</t>
+          <t>49793</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,73%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3316</t>
+          <t>3310</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14487</t>
+          <t>14720</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2257</t>
+          <t>2245</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12574</t>
+          <t>13428</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7492</t>
+          <t>8247</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>22783</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,48%</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4940</t>
+          <t>4853</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2517</t>
+          <t>2296</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13759</t>
+          <t>13264</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2919</t>
+          <t>2910</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13961</t>
+          <t>14571</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,07%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>900</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7560</t>
+          <t>7685</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2561</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13396</t>
+          <t>12473</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4423</t>
+          <t>4185</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>16848</t>
+          <t>17307</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,2%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>98846</t>
+          <t>98811</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>116225</t>
+          <t>117619</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>72,04%</t>
+          <t>72,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>85,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>123439</t>
+          <t>123307</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>150222</t>
+          <t>150857</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>59,12%</t>
+          <t>59,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>71,95%</t>
+          <t>72,26%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>227529</t>
+          <t>229278</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>260745</t>
+          <t>262009</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>65,76%</t>
+          <t>66,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>75,73%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>9286</t>
+          <t>8997</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>22650</t>
+          <t>23692</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>19148</t>
+          <t>19099</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>39440</t>
+          <t>39585</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>32554</t>
+          <t>32027</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>56737</t>
+          <t>57634</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,66%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2551</t>
+          <t>2531</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>11653</t>
+          <t>11669</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>17155</t>
+          <t>16897</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>36911</t>
+          <t>36654</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>21317</t>
+          <t>21942</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>43200</t>
+          <t>43557</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,59%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1619</t>
+          <t>1612</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9156</t>
+          <t>9089</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4834</t>
+          <t>4304</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>16871</t>
+          <t>16547</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>7993</t>
+          <t>7811</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>22236</t>
+          <t>22500</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,5%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>836</t>
+          <t>834</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7609</t>
+          <t>7545</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3447</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>15246</t>
+          <t>16348</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6545</t>
+          <t>6228</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>19364</t>
+          <t>19770</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>349507</t>
+          <t>349048</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>387323</t>
+          <t>388210</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>69,56%</t>
+          <t>69,47%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>77,08%</t>
+          <t>77,26%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>416568</t>
+          <t>416872</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>466891</t>
+          <t>467565</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>61,55%</t>
+          <t>61,59%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>68,98%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>783585</t>
+          <t>784663</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>846564</t>
+          <t>844615</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>66,44%</t>
+          <t>66,54%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>71,62%</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>54191</t>
+          <t>52962</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>84918</t>
+          <t>83890</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>89243</t>
+          <t>87911</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>127226</t>
+          <t>126236</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>149667</t>
+          <t>151409</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>198546</t>
+          <t>199983</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,96%</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>18223</t>
+          <t>18647</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>39547</t>
+          <t>39285</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>49585</t>
+          <t>50584</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>79493</t>
+          <t>81615</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>73686</t>
+          <t>73074</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>110932</t>
+          <t>110447</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,37%</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>12850</t>
+          <t>13329</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>29573</t>
+          <t>29482</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>17548</t>
+          <t>16925</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>39582</t>
+          <t>37917</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3850,12 +3850,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>34279</t>
+          <t>33358</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>60627</t>
+          <t>59021</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -3913,12 +3913,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>11014</t>
+          <t>11062</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>27032</t>
+          <t>27075</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3928,12 +3928,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>25012</t>
+          <t>25103</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>49328</t>
+          <t>50238</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3963,12 +3963,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>40948</t>
+          <t>40762</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>69230</t>
+          <t>68586</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -4375,12 +4375,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>94515</t>
+          <t>93885</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>114838</t>
+          <t>115188</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4390,12 +4390,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>67,73%</t>
+          <t>67,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>82,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>92276</t>
+          <t>92031</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>116348</t>
+          <t>116357</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4425,7 +4425,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>55,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>192553</t>
+          <t>192683</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>225389</t>
+          <t>226093</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4460,12 +4460,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>62,86%</t>
+          <t>62,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>73,81%</t>
         </is>
       </c>
     </row>
@@ -4488,12 +4488,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4617</t>
+          <t>5037</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17320</t>
+          <t>17125</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4503,12 +4503,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9946</t>
+          <t>9921</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26193</t>
+          <t>25529</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4538,12 +4538,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17856</t>
+          <t>18327</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>38210</t>
+          <t>38613</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,6%</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4601,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8229</t>
+          <t>8166</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23321</t>
+          <t>22612</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4616,12 +4616,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13036</t>
+          <t>13925</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>31062</t>
+          <t>30948</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>24797</t>
+          <t>24867</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>47892</t>
+          <t>47727</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,58%</t>
         </is>
       </c>
     </row>
@@ -4714,12 +4714,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1887</t>
+          <t>1111</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14808</t>
+          <t>13730</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4729,12 +4729,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6427</t>
+          <t>6087</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20674</t>
+          <t>19731</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10042</t>
+          <t>9969</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27238</t>
+          <t>28056</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,16%</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1992</t>
+          <t>1940</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11234</t>
+          <t>10562</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4842,12 +4842,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6279</t>
+          <t>6120</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>19322</t>
+          <t>18992</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>10301</t>
+          <t>10392</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>25223</t>
+          <t>26445</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,63%</t>
         </is>
       </c>
     </row>
@@ -5057,12 +5057,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>96259</t>
+          <t>97291</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>120274</t>
+          <t>120443</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>62,15%</t>
+          <t>62,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>87373</t>
+          <t>88486</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>117330</t>
+          <t>115131</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,64%</t>
+          <t>46,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,29%</t>
+          <t>60,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>191274</t>
+          <t>192503</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>228802</t>
+          <t>229390</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,23%</t>
+          <t>55,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>66,07%</t>
+          <t>66,24%</t>
         </is>
       </c>
     </row>
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4089</t>
+          <t>4219</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15716</t>
+          <t>16112</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19984</t>
+          <t>20262</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>40207</t>
+          <t>40102</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>27931</t>
+          <t>27089</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>50402</t>
+          <t>51304</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,81%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4179</t>
+          <t>4244</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15358</t>
+          <t>15684</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6551</t>
+          <t>6535</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>19666</t>
+          <t>20544</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>12697</t>
+          <t>12696</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>30544</t>
+          <t>30159</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5373,7 +5373,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,71%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8935</t>
+          <t>8966</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25127</t>
+          <t>25930</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5411,12 +5411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16264</t>
+          <t>17545</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38121</t>
+          <t>37172</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>30616</t>
+          <t>30643</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>56779</t>
+          <t>56070</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,19%</t>
         </is>
       </c>
     </row>
@@ -5509,12 +5509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6507</t>
+          <t>6588</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21950</t>
+          <t>21991</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5524,12 +5524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14587</t>
+          <t>13557</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>33132</t>
+          <t>31263</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>25756</t>
+          <t>24403</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>50113</t>
+          <t>47428</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>13,7%</t>
         </is>
       </c>
     </row>
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>65042</t>
+          <t>64542</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>85055</t>
+          <t>84971</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>62,78%</t>
+          <t>62,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>82,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>75508</t>
+          <t>75893</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>99240</t>
+          <t>100723</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>53,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>70,37%</t>
+          <t>71,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>147463</t>
+          <t>149351</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>179497</t>
+          <t>179418</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>60,28%</t>
+          <t>61,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>73,38%</t>
+          <t>73,35%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1093</t>
+          <t>1057</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12896</t>
+          <t>13904</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5926</t>
+          <t>5319</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20099</t>
+          <t>18715</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>8655</t>
+          <t>9301</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>25762</t>
+          <t>26635</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,89%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2522</t>
+          <t>2974</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13744</t>
+          <t>13496</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5252</t>
+          <t>5253</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>18917</t>
+          <t>17684</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6020,7 +6020,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>10513</t>
+          <t>9705</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>27148</t>
+          <t>27177</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,11%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4089</t>
+          <t>3169</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17423</t>
+          <t>16411</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7434</t>
+          <t>7384</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21249</t>
+          <t>20559</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>13727</t>
+          <t>13283</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>31712</t>
+          <t>33256</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,6%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3203</t>
+          <t>3168</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>16741</t>
+          <t>15510</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>10929</t>
+          <t>10958</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>28062</t>
+          <t>28661</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>16484</t>
+          <t>17352</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>38218</t>
+          <t>37351</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,27%</t>
         </is>
       </c>
     </row>
@@ -6421,12 +6421,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>106768</t>
+          <t>106442</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>131187</t>
+          <t>130006</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>66,06%</t>
+          <t>65,86%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>145844</t>
+          <t>146234</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>176357</t>
+          <t>176340</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>59,99%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>72,35%</t>
+          <t>72,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>262027</t>
+          <t>261639</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>299514</t>
+          <t>299341</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>64,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>73,89%</t>
+          <t>73,85%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5051</t>
+          <t>4997</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>17840</t>
+          <t>18572</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>24877</t>
+          <t>24854</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>47539</t>
+          <t>47114</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>33286</t>
+          <t>33249</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>59458</t>
+          <t>58496</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,43%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6120</t>
+          <t>6243</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>20961</t>
+          <t>21799</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>7137</t>
+          <t>7182</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>21656</t>
+          <t>21905</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>17335</t>
+          <t>16982</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>37738</t>
+          <t>38134</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,41%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5877</t>
+          <t>5825</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>20445</t>
+          <t>19447</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>9557</t>
+          <t>9332</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>26007</t>
+          <t>26122</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>17953</t>
+          <t>18619</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>39317</t>
+          <t>40517</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>10,0%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3027</t>
+          <t>3994</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>16475</t>
+          <t>16310</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>11192</t>
+          <t>10844</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>27161</t>
+          <t>27833</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6923,12 +6923,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>16592</t>
+          <t>16632</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>37348</t>
+          <t>38067</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,39%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>387230</t>
+          <t>387017</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>431970</t>
+          <t>431741</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>69,15%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>77,19%</t>
+          <t>77,15%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>426598</t>
+          <t>429223</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>482258</t>
+          <t>484289</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>57,77%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>64,91%</t>
+          <t>65,18%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>831877</t>
+          <t>832845</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>901880</t>
+          <t>901708</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>63,86%</t>
+          <t>63,94%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>69,22%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>22901</t>
+          <t>23281</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>46736</t>
+          <t>45741</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>75582</t>
+          <t>73932</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>112641</t>
+          <t>111442</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>104504</t>
+          <t>102540</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>148635</t>
+          <t>146729</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,26%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>31323</t>
+          <t>30542</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>56317</t>
+          <t>57445</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>43496</t>
+          <t>44256</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>74613</t>
+          <t>72248</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>82799</t>
+          <t>81371</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>121688</t>
+          <t>122123</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,38%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>29401</t>
+          <t>28027</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>55607</t>
+          <t>55453</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>52979</t>
+          <t>52718</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>84756</t>
+          <t>86074</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>87491</t>
+          <t>86851</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>129725</t>
+          <t>129034</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,91%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>22985</t>
+          <t>23339</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>47887</t>
+          <t>48620</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>54544</t>
+          <t>52794</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>87232</t>
+          <t>86327</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>84516</t>
+          <t>84710</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>128250</t>
+          <t>125360</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,62%</t>
         </is>
       </c>
     </row>
@@ -8017,12 +8017,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>100032</t>
+          <t>99912</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>117159</t>
+          <t>117833</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8032,12 +8032,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>73,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>99878</t>
+          <t>99942</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>125920</t>
+          <t>126469</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8067,12 +8067,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>57,6%</t>
+          <t>57,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>72,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8087,12 +8087,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>205589</t>
+          <t>204683</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>236595</t>
+          <t>238092</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8102,12 +8102,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>66,29%</t>
+          <t>66,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>76,77%</t>
         </is>
       </c>
     </row>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>815</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8266</t>
+          <t>8326</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8165,12 +8165,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11126</t>
+          <t>11527</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29069</t>
+          <t>29253</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8180,12 +8180,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13897</t>
+          <t>13940</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>33307</t>
+          <t>33038</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8215,12 +8215,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,65%</t>
         </is>
       </c>
     </row>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5305</t>
+          <t>5379</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16958</t>
+          <t>16287</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12769</t>
+          <t>12520</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>30471</t>
+          <t>30764</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>20930</t>
+          <t>21250</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>43535</t>
+          <t>42553</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>13,72%</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8356,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4412</t>
+          <t>4237</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14205</t>
+          <t>15311</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5459</t>
+          <t>5637</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19508</t>
+          <t>20069</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11748</t>
+          <t>12176</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30164</t>
+          <t>29456</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,5%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2456</t>
+          <t>2513</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11704</t>
+          <t>11691</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4636</t>
+          <t>4703</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>17868</t>
+          <t>17093</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>8582</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>24529</t>
+          <t>24320</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,84%</t>
         </is>
       </c>
     </row>
@@ -8699,12 +8699,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>113313</t>
+          <t>113272</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>134688</t>
+          <t>133080</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8714,12 +8714,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>68,7%</t>
+          <t>68,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8734,12 +8734,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>121099</t>
+          <t>123214</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>153158</t>
+          <t>153966</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8749,12 +8749,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>56,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>69,88%</t>
+          <t>70,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>241921</t>
+          <t>242807</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>281332</t>
+          <t>282183</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>62,98%</t>
+          <t>63,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>73,47%</t>
         </is>
       </c>
     </row>
@@ -8812,12 +8812,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7742</t>
+          <t>8135</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21362</t>
+          <t>21276</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8827,12 +8827,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8847,12 +8847,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17298</t>
+          <t>16470</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>36870</t>
+          <t>36986</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8862,12 +8862,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>28286</t>
+          <t>27327</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>53151</t>
+          <t>52662</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,71%</t>
         </is>
       </c>
     </row>
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6818</t>
+          <t>6755</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18996</t>
+          <t>20587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>16718</t>
+          <t>17576</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>38835</t>
+          <t>40619</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>28007</t>
+          <t>27624</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>52700</t>
+          <t>53169</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,84%</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4896</t>
+          <t>4333</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16429</t>
+          <t>16269</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12354</t>
+          <t>11331</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32152</t>
+          <t>31006</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9088,12 +9088,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19171</t>
+          <t>19030</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>41807</t>
+          <t>40933</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,66%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2587</t>
+          <t>2613</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12143</t>
+          <t>12952</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>3459</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>18031</t>
+          <t>17133</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7482</t>
+          <t>7312</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>24940</t>
+          <t>23596</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,14%</t>
         </is>
       </c>
     </row>
@@ -9381,12 +9381,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>78999</t>
+          <t>79146</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>96880</t>
+          <t>96780</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>68,67%</t>
+          <t>68,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>84,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9416,12 +9416,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>74491</t>
+          <t>75625</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>99921</t>
+          <t>100586</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>52,24%</t>
+          <t>53,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>70,07%</t>
+          <t>70,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>161108</t>
+          <t>160463</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>192690</t>
+          <t>192228</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9466,12 +9466,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>62,53%</t>
+          <t>62,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>74,61%</t>
         </is>
       </c>
     </row>
@@ -9494,12 +9494,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6754</t>
+          <t>6389</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19352</t>
+          <t>19097</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9509,12 +9509,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7377</t>
+          <t>7403</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22362</t>
+          <t>22453</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>16577</t>
+          <t>17166</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>36348</t>
+          <t>36955</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9579,12 +9579,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,34%</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9607,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1822</t>
+          <t>1794</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10941</t>
+          <t>11023</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8631</t>
+          <t>9385</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>26468</t>
+          <t>27197</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9657,12 +9657,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>13288</t>
+          <t>12830</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>33726</t>
+          <t>32915</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9692,12 +9692,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>12,78%</t>
         </is>
       </c>
     </row>
@@ -9720,12 +9720,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3491</t>
+          <t>3563</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14040</t>
+          <t>13789</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9735,12 +9735,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7779</t>
+          <t>7520</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24353</t>
+          <t>23523</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9770,12 +9770,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14267</t>
+          <t>13338</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>32790</t>
+          <t>32649</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,67%</t>
         </is>
       </c>
     </row>
@@ -9838,7 +9838,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7773</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9853,7 +9853,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3976</t>
+          <t>4859</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>17673</t>
+          <t>18582</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6016</t>
+          <t>5995</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>19885</t>
+          <t>20393</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,92%</t>
         </is>
       </c>
     </row>
@@ -10063,12 +10063,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>134320</t>
+          <t>133838</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>153519</t>
+          <t>153336</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10078,12 +10078,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>76,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>141905</t>
+          <t>143013</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>175632</t>
+          <t>175378</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10113,12 +10113,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>58,45%</t>
+          <t>58,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>72,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10133,12 +10133,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>283816</t>
+          <t>283713</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>322480</t>
+          <t>322197</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10148,12 +10148,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>68,0%</t>
+          <t>67,97%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>77,19%</t>
         </is>
       </c>
     </row>
@@ -10176,12 +10176,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2502</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>11876</t>
+          <t>11927</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10191,12 +10191,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>25338</t>
+          <t>24772</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>51194</t>
+          <t>49818</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10226,12 +10226,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10246,12 +10246,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>30821</t>
+          <t>31180</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>56970</t>
+          <t>58937</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10261,12 +10261,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>14,12%</t>
         </is>
       </c>
     </row>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8103</t>
+          <t>7883</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>22609</t>
+          <t>22142</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10304,12 +10304,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>7618</t>
+          <t>7595</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>23849</t>
+          <t>23027</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>17693</t>
+          <t>19333</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>39012</t>
+          <t>40484</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,7%</t>
         </is>
       </c>
     </row>
@@ -10402,12 +10402,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3471</t>
+          <t>3093</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>13298</t>
+          <t>12911</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10417,12 +10417,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10437,12 +10437,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>11066</t>
+          <t>10349</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>30660</t>
+          <t>30926</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>16737</t>
+          <t>17051</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>38806</t>
+          <t>38973</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,34%</t>
         </is>
       </c>
     </row>
@@ -10515,12 +10515,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>780</t>
+          <t>790</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>8906</t>
+          <t>9576</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10535,7 +10535,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10550,12 +10550,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>6027</t>
+          <t>6419</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>24404</t>
+          <t>25482</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>8551</t>
+          <t>8808</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>26527</t>
+          <t>28196</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,76%</t>
         </is>
       </c>
     </row>
@@ -10745,12 +10745,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>447386</t>
+          <t>448311</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>485687</t>
+          <t>485461</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10760,12 +10760,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>75,81%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>82,1%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10780,12 +10780,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>471482</t>
+          <t>472476</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>526834</t>
+          <t>529819</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>60,61%</t>
+          <t>60,73%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>67,72%</t>
+          <t>68,11%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>930435</t>
+          <t>936095</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1001458</t>
+          <t>1004925</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>68,37%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>73,14%</t>
+          <t>73,39%</t>
         </is>
       </c>
     </row>
@@ -10858,12 +10858,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>25483</t>
+          <t>25348</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>46963</t>
+          <t>46607</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10873,12 +10873,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>75655</t>
+          <t>78382</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>117029</t>
+          <t>116495</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>108426</t>
+          <t>106710</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>152714</t>
+          <t>151667</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,08%</t>
         </is>
       </c>
     </row>
@@ -10971,12 +10971,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>28794</t>
+          <t>30141</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>53869</t>
+          <t>53003</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>62970</t>
+          <t>61714</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>99627</t>
+          <t>97479</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>100410</t>
+          <t>97756</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>142731</t>
+          <t>139897</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,22%</t>
         </is>
       </c>
     </row>
@@ -11084,12 +11084,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>22612</t>
+          <t>22647</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>43734</t>
+          <t>42873</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11099,12 +11099,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11119,12 +11119,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>49893</t>
+          <t>47955</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>83183</t>
+          <t>82491</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11134,12 +11134,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11154,12 +11154,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>77475</t>
+          <t>78898</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>117537</t>
+          <t>117185</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,56%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>10612</t>
+          <t>10520</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>25052</t>
+          <t>26571</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>28883</t>
+          <t>28101</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>58050</t>
+          <t>57102</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>44181</t>
+          <t>42305</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>74064</t>
+          <t>75338</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -11654,32 +11654,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>97555</t>
+          <t>109411</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>87503</t>
+          <t>99429</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>106334</t>
+          <t>118686</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>65,88%</t>
+          <t>66,99%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>59,09%</t>
+          <t>60,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>71,81%</t>
+          <t>72,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11689,32 +11689,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>95063</t>
+          <t>101436</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>87148</t>
+          <t>92297</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>103151</t>
+          <t>110056</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>53,37%</t>
+          <t>53,44%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>48,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>57,91%</t>
+          <t>57,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11724,32 +11724,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>192617</t>
+          <t>210847</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>179536</t>
+          <t>196999</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>204337</t>
+          <t>223971</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>59,71%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
+          <t>55,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>62,64%</t>
+          <t>63,43%</t>
         </is>
       </c>
     </row>
@@ -11767,32 +11767,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13157</t>
+          <t>13926</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8760</t>
+          <t>8937</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20193</t>
+          <t>20679</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11802,17 +11802,17 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>20549</t>
+          <t>21907</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15660</t>
+          <t>16152</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26892</t>
+          <t>28652</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11822,7 +11822,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -11837,27 +11837,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>33706</t>
+          <t>35833</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>26635</t>
+          <t>28721</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>41343</t>
+          <t>44742</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -11880,32 +11880,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9929</t>
+          <t>10789</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5959</t>
+          <t>6890</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14896</t>
+          <t>16611</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11915,32 +11915,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>17927</t>
+          <t>19422</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13579</t>
+          <t>14357</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>24095</t>
+          <t>27139</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11950,32 +11950,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>27856</t>
+          <t>30211</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>21784</t>
+          <t>22557</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>35784</t>
+          <t>38696</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,96%</t>
         </is>
       </c>
     </row>
@@ -11993,22 +11993,22 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17742</t>
+          <t>19237</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12142</t>
+          <t>13395</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24778</t>
+          <t>27298</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -12018,7 +12018,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -12028,32 +12028,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>26805</t>
+          <t>28419</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20952</t>
+          <t>22592</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33119</t>
+          <t>35272</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -12063,32 +12063,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>44547</t>
+          <t>47656</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>36529</t>
+          <t>39265</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>55299</t>
+          <t>58452</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,55%</t>
         </is>
       </c>
     </row>
@@ -12106,32 +12106,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>9700</t>
+          <t>9951</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5868</t>
+          <t>5968</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15773</t>
+          <t>15759</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12141,32 +12141,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>17789</t>
+          <t>18619</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13031</t>
+          <t>13676</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>23210</t>
+          <t>24965</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12176,32 +12176,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>27490</t>
+          <t>28570</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>20702</t>
+          <t>21455</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>34232</t>
+          <t>36192</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,25%</t>
         </is>
       </c>
     </row>
@@ -12219,17 +12219,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>148083</t>
+          <t>163314</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>148083</t>
+          <t>163314</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>148083</t>
+          <t>163314</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -12254,17 +12254,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>178133</t>
+          <t>189803</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>178133</t>
+          <t>189803</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>178133</t>
+          <t>189803</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -12289,17 +12289,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>326216</t>
+          <t>353117</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>326216</t>
+          <t>353117</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>326216</t>
+          <t>353117</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -12336,32 +12336,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>118370</t>
+          <t>133066</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>108921</t>
+          <t>123015</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>125746</t>
+          <t>142420</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>73,93%</t>
+          <t>74,67%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>68,03%</t>
+          <t>69,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>79,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12371,32 +12371,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>126628</t>
+          <t>140491</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>116259</t>
+          <t>128811</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>136758</t>
+          <t>151521</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>58,21%</t>
+          <t>58,36%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>53,45%</t>
+          <t>53,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>62,87%</t>
+          <t>62,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12406,32 +12406,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>244998</t>
+          <t>273556</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>230460</t>
+          <t>257895</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>258598</t>
+          <t>287453</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>65,3%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>61,03%</t>
+          <t>61,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>68,48%</t>
+          <t>68,62%</t>
         </is>
       </c>
     </row>
@@ -12449,32 +12449,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12506</t>
+          <t>13502</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8154</t>
+          <t>8650</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19459</t>
+          <t>20288</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12484,32 +12484,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>26611</t>
+          <t>29273</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20253</t>
+          <t>21831</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>33666</t>
+          <t>36642</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12519,32 +12519,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>39117</t>
+          <t>42775</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>30396</t>
+          <t>34055</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>48091</t>
+          <t>51770</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,36%</t>
         </is>
       </c>
     </row>
@@ -12562,32 +12562,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9230</t>
+          <t>10143</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5570</t>
+          <t>5990</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15642</t>
+          <t>16606</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12597,32 +12597,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>19728</t>
+          <t>21616</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>14457</t>
+          <t>15846</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>25883</t>
+          <t>28157</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12632,32 +12632,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>28958</t>
+          <t>31759</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>22381</t>
+          <t>24219</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>37550</t>
+          <t>40967</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,78%</t>
         </is>
       </c>
     </row>
@@ -12675,32 +12675,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14469</t>
+          <t>15830</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9746</t>
+          <t>10470</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20908</t>
+          <t>23455</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12710,32 +12710,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>22974</t>
+          <t>26589</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17301</t>
+          <t>19912</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>29390</t>
+          <t>35138</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12745,32 +12745,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>37443</t>
+          <t>42418</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>29273</t>
+          <t>33605</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>46310</t>
+          <t>51400</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,27%</t>
         </is>
       </c>
     </row>
@@ -12788,32 +12788,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>5539</t>
+          <t>5663</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2778</t>
+          <t>2743</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10231</t>
+          <t>10598</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12823,32 +12823,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>21584</t>
+          <t>22759</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15795</t>
+          <t>16817</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>29810</t>
+          <t>30114</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12858,32 +12858,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>27123</t>
+          <t>28422</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>20345</t>
+          <t>21212</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>34965</t>
+          <t>37430</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>8,93%</t>
         </is>
       </c>
     </row>
@@ -12901,17 +12901,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>178204</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>178204</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>178204</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -12936,17 +12936,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>217525</t>
+          <t>240727</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>217525</t>
+          <t>240727</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>217525</t>
+          <t>240727</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12971,17 +12971,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>377640</t>
+          <t>418930</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>377640</t>
+          <t>418930</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>377640</t>
+          <t>418930</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -13018,32 +13018,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>107800</t>
+          <t>125919</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>98915</t>
+          <t>115130</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>115363</t>
+          <t>134138</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>79,58%</t>
+          <t>79,62%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>72,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13053,32 +13053,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>298793</t>
+          <t>106685</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>210723</t>
+          <t>96530</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>343080</t>
+          <t>116895</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>61,16%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>58,57%</t>
+          <t>55,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>67,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13088,32 +13088,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>406595</t>
+          <t>232604</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>337344</t>
+          <t>217898</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>458295</t>
+          <t>246845</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>69,94%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>68,11%</t>
+          <t>65,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>74,22%</t>
         </is>
       </c>
     </row>
@@ -13131,32 +13131,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>15267</t>
+          <t>18629</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9655</t>
+          <t>12521</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22147</t>
+          <t>27884</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13166,32 +13166,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>21366</t>
+          <t>24406</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>18230</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>54640</t>
+          <t>31921</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13201,32 +13201,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>36633</t>
+          <t>43035</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>13549</t>
+          <t>34059</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>67742</t>
+          <t>53007</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>15,94%</t>
         </is>
       </c>
     </row>
@@ -13244,32 +13244,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3970</t>
+          <t>4378</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1744</t>
+          <t>1759</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7700</t>
+          <t>10086</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13279,32 +13279,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>14075</t>
+          <t>15296</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3859</t>
+          <t>10499</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>36902</t>
+          <t>22006</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13314,32 +13314,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>18046</t>
+          <t>19674</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5757</t>
+          <t>13685</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>34586</t>
+          <t>27338</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>8,22%</t>
         </is>
       </c>
     </row>
@@ -13357,32 +13357,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4936</t>
+          <t>5515</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1965</t>
+          <t>2579</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9292</t>
+          <t>10902</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13392,32 +13392,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>10955</t>
+          <t>12480</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2470</t>
+          <t>7357</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>30247</t>
+          <t>19088</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13427,32 +13427,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>15890</t>
+          <t>17995</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5373</t>
+          <t>12178</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>30253</t>
+          <t>25898</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>7,79%</t>
         </is>
       </c>
     </row>
@@ -13470,32 +13470,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3486</t>
+          <t>3715</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>873</t>
+          <t>935</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8748</t>
+          <t>8321</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13505,32 +13505,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>14614</t>
+          <t>15574</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4055</t>
+          <t>9874</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>37040</t>
+          <t>22761</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13540,32 +13540,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>18100</t>
+          <t>19290</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5725</t>
+          <t>12790</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>35784</t>
+          <t>27253</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>8,19%</t>
         </is>
       </c>
     </row>
@@ -13583,17 +13583,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>135459</t>
+          <t>158157</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>135459</t>
+          <t>158157</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>135459</t>
+          <t>158157</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -13618,17 +13618,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>359803</t>
+          <t>174441</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>359803</t>
+          <t>174441</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>359803</t>
+          <t>174441</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -13653,17 +13653,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>495263</t>
+          <t>332598</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>495263</t>
+          <t>332598</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>495263</t>
+          <t>332598</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -13700,32 +13700,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>157674</t>
+          <t>166354</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>148546</t>
+          <t>157128</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>165985</t>
+          <t>175544</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>79,02%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>74,0%</t>
+          <t>74,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>83,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13735,32 +13735,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>167852</t>
+          <t>178845</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>155285</t>
+          <t>165701</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>179513</t>
+          <t>190389</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>61,31%</t>
+          <t>60,99%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>56,72%</t>
+          <t>56,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>65,57%</t>
+          <t>64,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13770,32 +13770,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>325526</t>
+          <t>345198</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>310575</t>
+          <t>329271</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>341166</t>
+          <t>361880</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>68,6%</t>
+          <t>68,52%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>65,45%</t>
+          <t>65,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>71,83%</t>
         </is>
       </c>
     </row>
@@ -13813,32 +13813,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>15444</t>
+          <t>15861</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>10063</t>
+          <t>10028</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>22311</t>
+          <t>22469</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13848,32 +13848,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>38285</t>
+          <t>39794</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>30662</t>
+          <t>32324</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>46534</t>
+          <t>48612</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13883,32 +13883,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>53729</t>
+          <t>55655</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>44530</t>
+          <t>45910</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>66280</t>
+          <t>67031</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,31%</t>
         </is>
       </c>
     </row>
@@ -13926,32 +13926,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>10307</t>
+          <t>10479</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6148</t>
+          <t>6521</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>16604</t>
+          <t>15948</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13961,32 +13961,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>27670</t>
+          <t>29552</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>20759</t>
+          <t>22393</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>36019</t>
+          <t>38250</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13996,32 +13996,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>37977</t>
+          <t>40031</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>29451</t>
+          <t>30990</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>47004</t>
+          <t>49798</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,88%</t>
         </is>
       </c>
     </row>
@@ -14039,32 +14039,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>11521</t>
+          <t>11604</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>7067</t>
+          <t>7304</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>17843</t>
+          <t>17548</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14074,32 +14074,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>24523</t>
+          <t>27828</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>17908</t>
+          <t>20808</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>33181</t>
+          <t>37818</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14109,32 +14109,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>36044</t>
+          <t>39431</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>27830</t>
+          <t>30082</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>45872</t>
+          <t>51181</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>10,16%</t>
         </is>
       </c>
     </row>
@@ -14152,32 +14152,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>5802</t>
+          <t>6234</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2707</t>
+          <t>3059</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>10639</t>
+          <t>11137</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14187,32 +14187,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>15432</t>
+          <t>17229</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>10370</t>
+          <t>11401</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>22342</t>
+          <t>25579</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14222,32 +14222,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>21234</t>
+          <t>23463</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>15461</t>
+          <t>16208</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>29234</t>
+          <t>32561</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,46%</t>
         </is>
       </c>
     </row>
@@ -14265,17 +14265,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>200748</t>
+          <t>210532</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>200748</t>
+          <t>210532</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>200748</t>
+          <t>210532</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -14300,17 +14300,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>273762</t>
+          <t>293247</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>273762</t>
+          <t>293247</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>273762</t>
+          <t>293247</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -14335,17 +14335,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>474510</t>
+          <t>503779</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>474510</t>
+          <t>503779</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>474510</t>
+          <t>503779</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -14382,32 +14382,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>481399</t>
+          <t>534750</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>463502</t>
+          <t>513174</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>498815</t>
+          <t>551253</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>75,29%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>71,93%</t>
+          <t>72,26%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -14417,32 +14417,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>688337</t>
+          <t>527456</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>595479</t>
+          <t>507958</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>849988</t>
+          <t>549256</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>58,72%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>57,86%</t>
+          <t>56,55%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>61,15%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -14452,32 +14452,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1169736</t>
+          <t>1062206</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1086845</t>
+          <t>1031392</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1328904</t>
+          <t>1090849</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>69,89%</t>
+          <t>66,04%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>64,12%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>67,82%</t>
         </is>
       </c>
     </row>
@@ -14495,32 +14495,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>56374</t>
+          <t>61919</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>44924</t>
+          <t>50203</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>68802</t>
+          <t>76329</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14530,32 +14530,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>106811</t>
+          <t>115380</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>53081</t>
+          <t>101647</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>139099</t>
+          <t>131004</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14565,32 +14565,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>163185</t>
+          <t>177298</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>107087</t>
+          <t>158457</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>194789</t>
+          <t>197699</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>12,29%</t>
         </is>
       </c>
     </row>
@@ -14608,32 +14608,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>33436</t>
+          <t>35789</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>25098</t>
+          <t>27557</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>42816</t>
+          <t>46772</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14643,32 +14643,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>79400</t>
+          <t>85886</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>40220</t>
+          <t>72996</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>104551</t>
+          <t>99816</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14678,32 +14678,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>112836</t>
+          <t>121676</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>75234</t>
+          <t>106066</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>135914</t>
+          <t>139371</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,67%</t>
         </is>
       </c>
     </row>
@@ -14721,32 +14721,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>48668</t>
+          <t>52186</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>38881</t>
+          <t>42393</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>60716</t>
+          <t>65052</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14756,32 +14756,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>85257</t>
+          <t>95315</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>45578</t>
+          <t>81683</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>113117</t>
+          <t>108723</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14791,32 +14791,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>133925</t>
+          <t>147500</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>88758</t>
+          <t>130300</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>159873</t>
+          <t>164443</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>10,22%</t>
         </is>
       </c>
     </row>
@@ -14834,32 +14834,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>24527</t>
+          <t>25564</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>17695</t>
+          <t>18283</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>32974</t>
+          <t>35104</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14869,32 +14869,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>69419</t>
+          <t>74181</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>36036</t>
+          <t>63349</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>92701</t>
+          <t>86937</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14904,32 +14904,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>93947</t>
+          <t>99744</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>61459</t>
+          <t>86104</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>114281</t>
+          <t>115164</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,16%</t>
         </is>
       </c>
     </row>
@@ -14947,17 +14947,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>644404</t>
+          <t>710207</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>644404</t>
+          <t>710207</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>644404</t>
+          <t>710207</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -14982,17 +14982,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>1029224</t>
+          <t>898218</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>1029224</t>
+          <t>898218</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1029224</t>
+          <t>898218</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -15017,17 +15017,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1673628</t>
+          <t>1608424</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1673628</t>
+          <t>1608424</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1673628</t>
+          <t>1608424</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
